--- a/TestData/TMTI0069005_VerifyClientNameIsAddedToTheProjectNamesForOpportunityEngagements.xlsx
+++ b/TestData/TMTI0069005_VerifyClientNameIsAddedToTheProjectNamesForOpportunityEngagements.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26501"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26731"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vijay.kumar\source\repos\SalesForce_Project\TestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\VKumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D78E61D-6BFD-4587-98ED-84E897ABCFDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCBD95CE-4443-4922-8B3F-5B5F1A8370F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="28890" windowHeight="14700" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="5" r:id="rId1"/>
@@ -64,13 +64,13 @@
     <t>Techno Coatings, Inc.</t>
   </si>
   <si>
-    <t>15012023090157</t>
-  </si>
-  <si>
-    <t>123421</t>
-  </si>
-  <si>
     <t>Time</t>
+  </si>
+  <si>
+    <t>125778</t>
+  </si>
+  <si>
+    <t>02192023111910</t>
   </si>
 </sst>
 </file>
@@ -402,18 +402,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.5546875" customWidth="1"/>
+    <col min="1" max="1" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -427,17 +427,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00E5A07C-950F-4461-89EE-53C28AB50916}">
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="31.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
@@ -451,11 +451,11 @@
         <v>10</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F1" s="1"/>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
@@ -473,7 +473,7 @@
       </c>
       <c r="F2" s="2"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>13</v>
       </c>
@@ -484,7 +484,7 @@
         <v>5</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>1</v>

--- a/TestData/TMTI0069005_VerifyClientNameIsAddedToTheProjectNamesForOpportunityEngagements.xlsx
+++ b/TestData/TMTI0069005_VerifyClientNameIsAddedToTheProjectNamesForOpportunityEngagements.xlsx
@@ -1,32 +1,43 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\VKumar0427\source\repos\SF_Automation\TestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCBD95CE-4443-4922-8B3F-5B5F1A8370F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57504F2E-D734-4657-B1BD-D0D67D71E9A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="28890" windowHeight="14700" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="5" r:id="rId1"/>
     <sheet name="SearchValue" sheetId="12" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="16">
   <si>
     <t>Global Search User</t>
   </si>
@@ -40,15 +51,9 @@
     <t>CompEye Profit Interest 409a 2023</t>
   </si>
   <si>
-    <t>Comprehensive EyeCare Partners LLC</t>
-  </si>
-  <si>
     <t>FVA</t>
   </si>
   <si>
-    <t>120781</t>
-  </si>
-  <si>
     <t>EngagementNo</t>
   </si>
   <si>
@@ -67,10 +72,19 @@
     <t>Time</t>
   </si>
   <si>
-    <t>125778</t>
-  </si>
-  <si>
-    <t>02192023111910</t>
+    <t>Omnicell GWI 2023</t>
+  </si>
+  <si>
+    <t>124833</t>
+  </si>
+  <si>
+    <t>Omnicell, Inc.</t>
+  </si>
+  <si>
+    <t>126683</t>
+  </si>
+  <si>
+    <t>NewOppTimeRecord</t>
   </si>
 </sst>
 </file>
@@ -426,65 +440,69 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00E5A07C-950F-4461-89EE-53C28AB50916}">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="31.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="31.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="5.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="31.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="F1" s="1"/>
     </row>
-    <row r="2" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" t="s">
-        <v>3</v>
+      <c r="D2" s="2" t="s">
+        <v>11</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>1</v>
       </c>
       <c r="F2" s="2"/>
+      <c r="G2" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>1</v>

--- a/TestData/TMTI0069005_VerifyClientNameIsAddedToTheProjectNamesForOpportunityEngagements.xlsx
+++ b/TestData/TMTI0069005_VerifyClientNameIsAddedToTheProjectNamesForOpportunityEngagements.xlsx
@@ -1,32 +1,43 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26501"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vijay.kumar\source\repos\SalesForce_Project\TestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D78E61D-6BFD-4587-98ED-84E897ABCFDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57504F2E-D734-4657-B1BD-D0D67D71E9A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="5" r:id="rId1"/>
     <sheet name="SearchValue" sheetId="12" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="16">
   <si>
     <t>Global Search User</t>
   </si>
@@ -40,15 +51,9 @@
     <t>CompEye Profit Interest 409a 2023</t>
   </si>
   <si>
-    <t>Comprehensive EyeCare Partners LLC</t>
-  </si>
-  <si>
     <t>FVA</t>
   </si>
   <si>
-    <t>120781</t>
-  </si>
-  <si>
     <t>EngagementNo</t>
   </si>
   <si>
@@ -64,13 +69,22 @@
     <t>Techno Coatings, Inc.</t>
   </si>
   <si>
-    <t>15012023090157</t>
-  </si>
-  <si>
-    <t>123421</t>
-  </si>
-  <si>
     <t>Time</t>
+  </si>
+  <si>
+    <t>Omnicell GWI 2023</t>
+  </si>
+  <si>
+    <t>124833</t>
+  </si>
+  <si>
+    <t>Omnicell, Inc.</t>
+  </si>
+  <si>
+    <t>126683</t>
+  </si>
+  <si>
+    <t>NewOppTimeRecord</t>
   </si>
 </sst>
 </file>
@@ -402,18 +416,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.5546875" customWidth="1"/>
+    <col min="1" max="1" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -426,65 +440,69 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00E5A07C-950F-4461-89EE-53C28AB50916}">
-  <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="31.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="31.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="31.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>14</v>
       </c>
       <c r="F1" s="1"/>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" t="s">
-        <v>3</v>
+      <c r="D2" s="2" t="s">
+        <v>11</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>1</v>
       </c>
       <c r="F2" s="2"/>
+      <c r="G2" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>1</v>
